--- a/public/assets/documents/excel/sample_upload/Unit.xlsx
+++ b/public/assets/documents/excel/sample_upload/Unit.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xampp\82\htdocs\NeoEHS_Karam\public\assets\documents\excel\sample_upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xampp8.2\htdocs\NeoEHS\NeoEHS_Karam\public\assets\documents\excel\sample_upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>SNo</t>
   </si>
@@ -31,26 +32,11 @@
   <si>
     <t>Unit Name</t>
   </si>
-  <si>
-    <t>Type One Company</t>
-  </si>
-  <si>
-    <t>Location 1</t>
-  </si>
-  <si>
-    <t>unit1</t>
-  </si>
-  <si>
-    <t>Location2</t>
-  </si>
-  <si>
-    <t>unit2</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -70,7 +56,13 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -87,6 +79,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -95,10 +95,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -344,18 +344,21 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="8.886719" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="3" width="17.10938" customWidth="1"/>
-    <col min="4" max="4" width="12.14063" customWidth="1"/>
+    <col min="2" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -369,34 +372,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
